--- a/docagent_clean_mvp/sample_data/raw_excels/VSA_SetB.xlsx
+++ b/docagent_clean_mvp/sample_data/raw_excels/VSA_SetB.xlsx
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Critical vulnerabilities identified by external scanning are remediated within 15 days of disclosure.</t>
+          <t>Standard Vulnerability Management control mandates that critical vulnerabilities identified by external scanning are remediated within 15 days of disclosure. [VSA-023]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>In progress - 2 of 3 open items within SLA</t>
+          <t>Pending - awaiting evidence upload</t>
         </is>
       </c>
     </row>
